--- a/DATA/MACHINE_LEARNING/C13_MACHINE_LEARNING/Transformaciones/Exp04/registro_preparacion.xlsx
+++ b/DATA/MACHINE_LEARNING/C13_MACHINE_LEARNING/Transformaciones/Exp04/registro_preparacion.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EXP_01</t>
+          <t>Exp04</t>
         </is>
       </c>
     </row>

--- a/DATA/MACHINE_LEARNING/C13_MACHINE_LEARNING/Transformaciones/Exp04/registro_preparacion.xlsx
+++ b/DATA/MACHINE_LEARNING/C13_MACHINE_LEARNING/Transformaciones/Exp04/registro_preparacion.xlsx
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>516</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
